--- a/data/游戏配置表.xlsx
+++ b/data/游戏配置表.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="210">
   <si>
     <t>角色名称</t>
   </si>
@@ -76,9 +76,6 @@
     <t>手动</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>镜换者</t>
   </si>
   <si>
@@ -148,6 +145,12 @@
     <t>jianzao</t>
   </si>
   <si>
+    <t>积怨者</t>
+  </si>
+  <si>
+    <t>jiyuan</t>
+  </si>
+  <si>
     <t>技能等级</t>
   </si>
   <si>
@@ -322,6 +325,9 @@
     <t>初始生命值</t>
   </si>
   <si>
+    <t>60</t>
+  </si>
+  <si>
     <t>开局实际HP（而非最大值）</t>
   </si>
   <si>
@@ -334,24 +340,36 @@
     <t>裂缝基础能量</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>每个裂缝提供的基础能量加成</t>
   </si>
   <si>
     <t>裂缝能量递增</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>每多一个裂缝，加成额外增加的量</t>
   </si>
   <si>
     <t>普通技能消耗</t>
   </si>
   <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>开启裂缝消耗的能量</t>
   </si>
   <si>
     <t>强化技能消耗</t>
   </si>
   <si>
+    <t>30</t>
+  </si>
+  <si>
     <t>强化裂缝消耗的能量</t>
   </si>
   <si>
@@ -364,6 +382,9 @@
     <t>超能解放能量阈值</t>
   </si>
   <si>
+    <t>100</t>
+  </si>
+  <si>
     <t>能量达到此值时触发超能解放</t>
   </si>
   <si>
@@ -403,6 +424,9 @@
     <t>受伤牌面加成阈值</t>
   </si>
   <si>
+    <t>50</t>
+  </si>
+  <si>
     <t>累计受伤达到此值后，牌面获得加成</t>
   </si>
   <si>
@@ -421,24 +445,30 @@
     <t>吸血激活点数</t>
   </si>
   <si>
+    <t>25</t>
+  </si>
+  <si>
     <t>激活吸血需要的合成点数</t>
   </si>
   <si>
-    <t>使用强化技能需要的合成点数</t>
+    <t>强化技能攻击加成</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>使用强化技能时额外攻击伤害</t>
   </si>
   <si>
     <t>强化技能自伤</t>
   </si>
   <si>
+    <t>20</t>
+  </si>
+  <si>
     <t>使用强化技能时自伤的HP</t>
   </si>
   <si>
-    <t>强化技能攻击加成</t>
-  </si>
-  <si>
-    <t>使用强化技能时额外攻击伤害</t>
-  </si>
-  <si>
     <t>普通技能自伤</t>
   </si>
   <si>
@@ -454,16 +484,22 @@
     <t>反弹层数上限</t>
   </si>
   <si>
+    <t>5</t>
+  </si>
+  <si>
     <t>反伤护盾可叠加的最大层数</t>
   </si>
   <si>
-    <t>叠加1层反弹护盾消耗的能量</t>
-  </si>
-  <si>
-    <t>技能免疫消耗的能量</t>
-  </si>
-  <si>
-    <t>使用强化技能需要的最低点数</t>
+    <t>解放技能消耗</t>
+  </si>
+  <si>
+    <t>解放技能消耗的能量</t>
+  </si>
+  <si>
+    <t>解放技能点数阈值</t>
+  </si>
+  <si>
+    <t>触发解放需要的最低技能牌点数</t>
   </si>
   <si>
     <t>强化免疫阶段数</t>
@@ -472,27 +508,18 @@
     <t>技能免疫持续的阶段数</t>
   </si>
   <si>
-    <t>解放技能消耗</t>
-  </si>
-  <si>
-    <t>解放技能消耗的能量</t>
-  </si>
-  <si>
-    <t>解放技能点数阈值</t>
-  </si>
-  <si>
-    <t>触发解放需要的最低技能牌点数</t>
-  </si>
-  <si>
     <t>解放免疫阶段数</t>
   </si>
   <si>
-    <t>全免疫+反弹持续的阶段数（约2回合）</t>
+    <t>全免疫+反弹持续的阶段数</t>
   </si>
   <si>
     <t>工人基础效率</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>每个小人每阶段建造的进度（基础值）</t>
   </si>
   <si>
@@ -533,6 +560,18 @@
   </si>
   <si>
     <t>触发解放的最高技能牌点数</t>
+  </si>
+  <si>
+    <t>解锁伤害阈值</t>
+  </si>
+  <si>
+    <t>任一原始牌型累计伤害达到此值，该牌型攻击转为不可防御</t>
+  </si>
+  <si>
+    <t>解锁后补抽数</t>
+  </si>
+  <si>
+    <t>解锁牌型成功命中后补抽的牌数</t>
   </si>
   <si>
     <t>场地名称</t>
@@ -682,11 +721,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true" applyAlignment="false">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment vertical="top" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true" applyAlignment="false">
-      <alignment/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1044,19 +1083,13 @@
       <c r="G3">
         <v>1</v>
       </c>
-      <c r="H3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
         <v>20</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
       </c>
       <c r="C4">
         <v>90</v>
@@ -1070,22 +1103,16 @@
       <c r="F4" t="s">
         <v>18</v>
       </c>
-      <c r="G4" t="s">
-        <v>19</v>
-      </c>
       <c r="H4">
         <v>1</v>
       </c>
-      <c r="I4" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
         <v>22</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
       </c>
       <c r="C5">
         <v>95</v>
@@ -1099,22 +1126,13 @@
       <c r="F5" t="s">
         <v>18</v>
       </c>
-      <c r="G5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I5" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
         <v>24</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
       </c>
       <c r="C6">
         <v>95</v>
@@ -1128,22 +1146,13 @@
       <c r="F6" t="s">
         <v>18</v>
       </c>
-      <c r="G6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" t="s">
-        <v>19</v>
-      </c>
-      <c r="I6" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
         <v>26</v>
-      </c>
-      <c r="B7" t="s">
-        <v>27</v>
       </c>
       <c r="C7">
         <v>85</v>
@@ -1160,19 +1169,13 @@
       <c r="G7">
         <v>2</v>
       </c>
-      <c r="H7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I7" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
         <v>28</v>
-      </c>
-      <c r="B8" t="s">
-        <v>29</v>
       </c>
       <c r="C8">
         <v>110</v>
@@ -1184,24 +1187,18 @@
         <v>80</v>
       </c>
       <c r="F8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8" t="s">
         <v>30</v>
-      </c>
-      <c r="G8" t="s">
-        <v>19</v>
-      </c>
-      <c r="H8" t="s">
-        <v>19</v>
-      </c>
-      <c r="I8" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s">
         <v>32</v>
-      </c>
-      <c r="B9" t="s">
-        <v>33</v>
       </c>
       <c r="C9">
         <v>150</v>
@@ -1213,24 +1210,15 @@
         <v>0</v>
       </c>
       <c r="F9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G9" t="s">
-        <v>19</v>
-      </c>
-      <c r="H9" t="s">
-        <v>19</v>
-      </c>
-      <c r="I9" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" t="s">
         <v>35</v>
-      </c>
-      <c r="B10" t="s">
-        <v>36</v>
       </c>
       <c r="C10">
         <v>80</v>
@@ -1242,24 +1230,15 @@
         <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>34</v>
-      </c>
-      <c r="G10" t="s">
-        <v>19</v>
-      </c>
-      <c r="H10" t="s">
-        <v>19</v>
-      </c>
-      <c r="I10" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" t="s">
         <v>37</v>
-      </c>
-      <c r="B11" t="s">
-        <v>38</v>
       </c>
       <c r="C11">
         <v>90</v>
@@ -1271,24 +1250,15 @@
         <v>0</v>
       </c>
       <c r="F11" t="s">
-        <v>34</v>
-      </c>
-      <c r="G11" t="s">
-        <v>19</v>
-      </c>
-      <c r="H11" t="s">
-        <v>19</v>
-      </c>
-      <c r="I11" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" t="s">
         <v>39</v>
-      </c>
-      <c r="B12" t="s">
-        <v>40</v>
       </c>
       <c r="C12">
         <v>95</v>
@@ -1300,24 +1270,15 @@
         <v>0</v>
       </c>
       <c r="F12" t="s">
-        <v>34</v>
-      </c>
-      <c r="G12" t="s">
-        <v>19</v>
-      </c>
-      <c r="H12" t="s">
-        <v>19</v>
-      </c>
-      <c r="I12" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" t="s">
         <v>41</v>
-      </c>
-      <c r="B13" t="s">
-        <v>42</v>
       </c>
       <c r="C13">
         <v>90</v>
@@ -1329,16 +1290,27 @@
         <v>0</v>
       </c>
       <c r="F13" t="s">
-        <v>34</v>
-      </c>
-      <c r="G13" t="s">
-        <v>19</v>
-      </c>
-      <c r="H13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I13" t="s">
-        <v>19</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14">
+        <v>85</v>
+      </c>
+      <c r="D14">
+        <v>100</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1361,42 +1333,42 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>11</v>
@@ -1417,7 +1389,7 @@
         <v>14</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3">
@@ -1425,10 +1397,10 @@
         <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D3">
         <v>10</v>
@@ -1436,20 +1408,8 @@
       <c r="E3">
         <v>8</v>
       </c>
-      <c r="F3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" t="s">
-        <v>19</v>
-      </c>
       <c r="J3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4">
@@ -1457,10 +1417,10 @@
         <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D4">
         <v>20</v>
@@ -1468,20 +1428,8 @@
       <c r="E4">
         <v>16</v>
       </c>
-      <c r="F4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4" t="s">
-        <v>19</v>
-      </c>
       <c r="J4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5">
@@ -1489,10 +1437,10 @@
         <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D5">
         <v>80</v>
@@ -1503,72 +1451,54 @@
       <c r="F5">
         <v>20</v>
       </c>
-      <c r="G5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I5" t="s">
-        <v>19</v>
-      </c>
       <c r="J5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D7">
         <v>8</v>
       </c>
-      <c r="E7" t="s">
-        <v>19</v>
-      </c>
       <c r="F7">
         <v>5</v>
       </c>
-      <c r="G7" t="s">
-        <v>19</v>
-      </c>
       <c r="H7">
         <v>2</v>
       </c>
-      <c r="I7" t="s">
-        <v>19</v>
-      </c>
       <c r="J7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D8">
         <v>16</v>
@@ -1576,31 +1506,22 @@
       <c r="E8">
         <v>10</v>
       </c>
-      <c r="F8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8" t="s">
-        <v>19</v>
-      </c>
       <c r="H8">
         <v>3</v>
       </c>
-      <c r="I8" t="s">
-        <v>19</v>
-      </c>
       <c r="J8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D9">
         <v>80</v>
@@ -1611,72 +1532,54 @@
       <c r="F9">
         <v>20</v>
       </c>
-      <c r="G9" t="s">
-        <v>19</v>
-      </c>
       <c r="H9">
         <v>2</v>
       </c>
-      <c r="I9" t="s">
-        <v>19</v>
-      </c>
       <c r="J9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D11" s="4">
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D11">
         <v>5</v>
-      </c>
-      <c r="E11" t="s">
-        <v>19</v>
-      </c>
-      <c r="F11" t="s">
-        <v>19</v>
       </c>
       <c r="G11">
         <v>20</v>
       </c>
-      <c r="H11" t="s">
-        <v>19</v>
-      </c>
-      <c r="I11" t="s">
-        <v>19</v>
-      </c>
       <c r="J11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D12">
         <v>10</v>
@@ -1684,31 +1587,22 @@
       <c r="E12">
         <v>8</v>
       </c>
-      <c r="F12" t="s">
-        <v>19</v>
-      </c>
       <c r="G12">
         <v>30</v>
       </c>
-      <c r="H12" t="s">
-        <v>19</v>
-      </c>
-      <c r="I12" t="s">
-        <v>19</v>
-      </c>
       <c r="J12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D13">
         <v>60</v>
@@ -1722,37 +1616,31 @@
       <c r="G13">
         <v>20</v>
       </c>
-      <c r="H13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I13" t="s">
-        <v>19</v>
-      </c>
       <c r="J13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D15">
         <v>10</v>
@@ -1763,28 +1651,19 @@
       <c r="F15">
         <v>6</v>
       </c>
-      <c r="G15" t="s">
-        <v>19</v>
-      </c>
-      <c r="H15" t="s">
-        <v>19</v>
-      </c>
-      <c r="I15" t="s">
-        <v>19</v>
-      </c>
       <c r="J15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D16">
         <v>20</v>
@@ -1795,30 +1674,21 @@
       <c r="F16">
         <v>10</v>
       </c>
-      <c r="G16" t="s">
-        <v>19</v>
-      </c>
-      <c r="H16" t="s">
-        <v>19</v>
-      </c>
-      <c r="I16" t="s">
-        <v>19</v>
-      </c>
       <c r="J16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D17" s="4">
+      <c r="A17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17">
         <v>80</v>
       </c>
       <c r="E17">
@@ -1827,40 +1697,31 @@
       <c r="F17">
         <v>20</v>
       </c>
-      <c r="G17" t="s">
-        <v>19</v>
-      </c>
-      <c r="H17" t="s">
-        <v>19</v>
-      </c>
-      <c r="I17" t="s">
-        <v>19</v>
-      </c>
       <c r="J17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D19">
         <v>10</v>
@@ -1868,31 +1729,19 @@
       <c r="E19">
         <v>10</v>
       </c>
-      <c r="F19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G19" t="s">
-        <v>19</v>
-      </c>
-      <c r="H19" t="s">
-        <v>19</v>
-      </c>
-      <c r="I19" t="s">
-        <v>19</v>
-      </c>
       <c r="J19" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D20">
         <v>20</v>
@@ -1900,31 +1749,19 @@
       <c r="E20">
         <v>20</v>
       </c>
-      <c r="F20" t="s">
-        <v>19</v>
-      </c>
-      <c r="G20" t="s">
-        <v>19</v>
-      </c>
-      <c r="H20" t="s">
-        <v>19</v>
-      </c>
-      <c r="I20" t="s">
-        <v>19</v>
-      </c>
       <c r="J20" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D21">
         <v>80</v>
@@ -1932,113 +1769,74 @@
       <c r="E21">
         <v>40</v>
       </c>
-      <c r="F21" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" t="s">
-        <v>19</v>
-      </c>
-      <c r="H21" t="s">
-        <v>19</v>
-      </c>
-      <c r="I21" t="s">
-        <v>19</v>
-      </c>
       <c r="J21" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C23" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D23">
         <v>8</v>
       </c>
-      <c r="E23" t="s">
-        <v>19</v>
-      </c>
       <c r="F23">
         <v>10</v>
       </c>
-      <c r="G23" t="s">
-        <v>19</v>
-      </c>
-      <c r="H23" t="s">
-        <v>19</v>
-      </c>
-      <c r="I23" t="s">
-        <v>19</v>
-      </c>
       <c r="J23" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B24" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D24">
         <v>16</v>
       </c>
-      <c r="E24" t="s">
-        <v>19</v>
-      </c>
       <c r="F24">
         <v>20</v>
       </c>
       <c r="G24">
         <v>10</v>
       </c>
-      <c r="H24" t="s">
-        <v>19</v>
-      </c>
-      <c r="I24" t="s">
-        <v>19</v>
-      </c>
       <c r="J24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C25" t="s">
-        <v>93</v>
-      </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
-      <c r="E25" t="s">
-        <v>19</v>
+        <v>94</v>
       </c>
       <c r="F25">
         <v>30</v>
@@ -2046,57 +1844,9 @@
       <c r="G25">
         <v>10</v>
       </c>
-      <c r="H25" t="s">
-        <v>19</v>
-      </c>
-      <c r="I25" t="s">
-        <v>19</v>
-      </c>
       <c r="J25" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
+        <v>95</v>
+      </c>
     </row>
   </sheetData>
 </worksheet>
@@ -2117,559 +1867,631 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>99</v>
+        <v>30</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C3">
-        <v>60</v>
-      </c>
-      <c r="D3" s="3" t="s">
         <v>101</v>
+      </c>
+      <c r="C3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C4" t="s">
         <v>102</v>
       </c>
-      <c r="C4">
-        <v>60</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>103</v>
+      <c r="D4" s="4" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="C5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
+      </c>
+      <c r="C6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>108</v>
-      </c>
-      <c r="C7">
-        <v>15</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
+      </c>
+      <c r="C7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>110</v>
-      </c>
-      <c r="C8">
-        <v>30</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
+      </c>
+      <c r="C8" t="s">
+        <v>116</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>112</v>
-      </c>
-      <c r="C9">
-        <v>3</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>113</v>
+        <v>118</v>
+      </c>
+      <c r="C9" t="s">
+        <v>107</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>114</v>
-      </c>
-      <c r="C10">
-        <v>100</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>115</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="C10" t="s">
+        <v>121</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B12" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>117</v>
+        <v>30</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="C13" t="s">
-        <v>119</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>120</v>
+        <v>126</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>121</v>
-      </c>
-      <c r="C14">
-        <v>2</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>122</v>
+        <v>128</v>
+      </c>
+      <c r="C14" t="s">
+        <v>110</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B15" t="s">
-        <v>123</v>
-      </c>
-      <c r="C15">
-        <v>2</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>124</v>
+        <v>130</v>
+      </c>
+      <c r="C15" t="s">
+        <v>110</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B16" t="s">
-        <v>125</v>
-      </c>
-      <c r="C16">
-        <v>2</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>126</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="C16" t="s">
+        <v>110</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B18" t="s">
-        <v>127</v>
-      </c>
-      <c r="C18">
-        <v>50</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
+      </c>
+      <c r="C18" t="s">
+        <v>107</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B19" t="s">
-        <v>129</v>
-      </c>
-      <c r="C19">
-        <v>3</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>130</v>
+        <v>134</v>
+      </c>
+      <c r="C19" t="s">
+        <v>135</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s">
-        <v>131</v>
-      </c>
-      <c r="C20">
-        <v>30</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
+      </c>
+      <c r="C20" t="s">
+        <v>107</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B21" t="s">
-        <v>133</v>
-      </c>
-      <c r="C21">
-        <v>25</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
+      </c>
+      <c r="C21" t="s">
+        <v>116</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B22" t="s">
-        <v>112</v>
-      </c>
-      <c r="C22">
-        <v>3</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>135</v>
+        <v>141</v>
+      </c>
+      <c r="C22" t="s">
+        <v>142</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B23" t="s">
-        <v>136</v>
-      </c>
-      <c r="C23">
-        <v>20</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>137</v>
+        <v>144</v>
+      </c>
+      <c r="C23" t="s">
+        <v>145</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B24" t="s">
-        <v>138</v>
-      </c>
-      <c r="C24">
-        <v>10</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>139</v>
+        <v>147</v>
+      </c>
+      <c r="C24" t="s">
+        <v>148</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B25" t="s">
-        <v>140</v>
-      </c>
-      <c r="C25">
-        <v>10</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>141</v>
+        <v>150</v>
+      </c>
+      <c r="C25" t="s">
+        <v>145</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B26" t="s">
-        <v>142</v>
-      </c>
-      <c r="C26">
-        <v>2</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>143</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="C26" t="s">
+        <v>110</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B28" t="s">
-        <v>144</v>
-      </c>
-      <c r="C28">
-        <v>5</v>
-      </c>
-      <c r="D28" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C28" t="s">
         <v>145</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B29" t="s">
-        <v>108</v>
-      </c>
-      <c r="C29">
-        <v>10</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>146</v>
+        <v>115</v>
+      </c>
+      <c r="C29" t="s">
+        <v>113</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B30" t="s">
-        <v>110</v>
-      </c>
-      <c r="C30">
-        <v>15</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>147</v>
+        <v>118</v>
+      </c>
+      <c r="C30" t="s">
+        <v>107</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>112</v>
-      </c>
-      <c r="C31">
-        <v>3</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>148</v>
+        <v>154</v>
+      </c>
+      <c r="C31" t="s">
+        <v>155</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>149</v>
-      </c>
-      <c r="C32">
-        <v>3</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>150</v>
+        <v>157</v>
+      </c>
+      <c r="C32" t="s">
+        <v>135</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>151</v>
-      </c>
-      <c r="C33">
-        <v>50</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>152</v>
+        <v>159</v>
+      </c>
+      <c r="C33" t="s">
+        <v>142</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B34" t="s">
-        <v>153</v>
-      </c>
-      <c r="C34">
-        <v>25</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>154</v>
+        <v>161</v>
+      </c>
+      <c r="C34" t="s">
+        <v>107</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B35" t="s">
-        <v>155</v>
-      </c>
-      <c r="C35">
-        <v>10</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>156</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="C35" t="s">
+        <v>145</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B37" t="s">
-        <v>157</v>
-      </c>
-      <c r="C37">
-        <v>1</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>158</v>
+        <v>165</v>
+      </c>
+      <c r="C37" t="s">
+        <v>166</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" t="s">
-        <v>159</v>
-      </c>
-      <c r="C38">
-        <v>2</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>160</v>
+        <v>168</v>
+      </c>
+      <c r="C38" t="s">
+        <v>110</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>161</v>
-      </c>
-      <c r="C39">
-        <v>2</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>162</v>
+        <v>170</v>
+      </c>
+      <c r="C39" t="s">
+        <v>110</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>163</v>
-      </c>
-      <c r="C40">
-        <v>5</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>164</v>
+        <v>172</v>
+      </c>
+      <c r="C40" t="s">
+        <v>155</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>165</v>
-      </c>
-      <c r="C41">
-        <v>20</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>166</v>
+        <v>174</v>
+      </c>
+      <c r="C41" t="s">
+        <v>148</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>167</v>
-      </c>
-      <c r="C42">
-        <v>5</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>168</v>
+        <v>176</v>
+      </c>
+      <c r="C42" t="s">
+        <v>155</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>169</v>
-      </c>
-      <c r="C43">
-        <v>20</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>154</v>
+        <v>178</v>
+      </c>
+      <c r="C43" t="s">
+        <v>148</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>170</v>
-      </c>
-      <c r="C44">
-        <v>25</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>171</v>
+        <v>179</v>
+      </c>
+      <c r="C44" t="s">
+        <v>142</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>42</v>
+      </c>
+      <c r="B46" t="s">
+        <v>123</v>
+      </c>
+      <c r="C46" t="s">
+        <v>30</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47" t="s">
+        <v>181</v>
+      </c>
+      <c r="C47" t="s">
+        <v>135</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" t="s">
+        <v>183</v>
+      </c>
+      <c r="C48" t="s">
+        <v>110</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -2686,28 +2508,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2">
@@ -2724,7 +2546,7 @@
         <v>15</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>15</v>
@@ -2738,207 +2560,102 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="B3" t="s">
-        <v>182</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>19</v>
+        <v>195</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
-      <c r="F3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="B4" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
-      <c r="F4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="B5" t="s">
-        <v>186</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
+        <v>199</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="B6" t="s">
-        <v>188</v>
-      </c>
-      <c r="C6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" t="s">
-        <v>19</v>
+        <v>201</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
-      <c r="F6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="B7" t="s">
-        <v>190</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" t="s">
-        <v>19</v>
+        <v>203</v>
       </c>
       <c r="E7">
         <v>2</v>
       </c>
-      <c r="F7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="B8" t="s">
-        <v>192</v>
-      </c>
-      <c r="C8" t="s">
-        <v>19</v>
+        <v>205</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8" t="s">
-        <v>19</v>
-      </c>
-      <c r="H8" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="B9" t="s">
-        <v>194</v>
-      </c>
-      <c r="C9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" t="s">
-        <v>19</v>
+        <v>207</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
-      <c r="F9" t="s">
-        <v>19</v>
-      </c>
       <c r="G9">
         <v>1</v>
       </c>
-      <c r="H9" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="B10" t="s">
-        <v>196</v>
-      </c>
-      <c r="C10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" t="s">
-        <v>19</v>
+        <v>209</v>
       </c>
       <c r="E10">
         <v>0</v>
-      </c>
-      <c r="F10" t="s">
-        <v>19</v>
-      </c>
-      <c r="G10" t="s">
-        <v>19</v>
       </c>
       <c r="H10">
         <v>15</v>

--- a/data/游戏配置表.xlsx
+++ b/data/游戏配置表.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="240">
   <si>
     <t>角色名称</t>
   </si>
@@ -67,43 +67,43 @@
     <t>是/否</t>
   </si>
   <si>
-    <t>力裁者</t>
-  </si>
-  <si>
-    <t>licai</t>
+    <t>焰</t>
+  </si>
+  <si>
+    <t>homura</t>
   </si>
   <si>
     <t>手动</t>
   </si>
   <si>
-    <t>镜换者</t>
-  </si>
-  <si>
-    <t>jinghuan</t>
-  </si>
-  <si>
-    <t>空手者</t>
-  </si>
-  <si>
-    <t>kongshou</t>
-  </si>
-  <si>
-    <t>噬渊者</t>
-  </si>
-  <si>
-    <t>shiyuan</t>
-  </si>
-  <si>
-    <t>灼血者</t>
-  </si>
-  <si>
-    <t>zhuoxue</t>
-  </si>
-  <si>
-    <t>殉道者</t>
-  </si>
-  <si>
-    <t>xundao</t>
+    <t>镜花</t>
+  </si>
+  <si>
+    <t>kyoka</t>
+  </si>
+  <si>
+    <t>空音</t>
+  </si>
+  <si>
+    <t>sorane</t>
+  </si>
+  <si>
+    <t>深宵</t>
+  </si>
+  <si>
+    <t>miyako</t>
+  </si>
+  <si>
+    <t>茜</t>
+  </si>
+  <si>
+    <t>akane</t>
+  </si>
+  <si>
+    <t>圣罗</t>
+  </si>
+  <si>
+    <t>seira</t>
   </si>
   <si>
     <t>自动</t>
@@ -112,61 +112,67 @@
     <t>是</t>
   </si>
   <si>
-    <t>时空裂缝者</t>
-  </si>
-  <si>
-    <t>liewen</t>
+    <t>时雨</t>
+  </si>
+  <si>
+    <t>shigure</t>
   </si>
   <si>
     <t>无</t>
   </si>
   <si>
-    <t>万能者</t>
-  </si>
-  <si>
-    <t>wanneng</t>
-  </si>
-  <si>
-    <t>血魔</t>
-  </si>
-  <si>
-    <t>xuemo</t>
-  </si>
-  <si>
-    <t>反伤者</t>
-  </si>
-  <si>
-    <t>fanshang</t>
-  </si>
-  <si>
-    <t>建造者</t>
-  </si>
-  <si>
-    <t>jianzao</t>
-  </si>
-  <si>
-    <t>积怨者</t>
-  </si>
-  <si>
-    <t>jiyuan</t>
-  </si>
-  <si>
-    <t>明暗者</t>
-  </si>
-  <si>
-    <t>mingan</t>
-  </si>
-  <si>
-    <t>刻印者</t>
-  </si>
-  <si>
-    <t>keyin</t>
-  </si>
-  <si>
-    <t>节律者</t>
-  </si>
-  <si>
-    <t>jielv</t>
+    <t>梦月</t>
+  </si>
+  <si>
+    <t>mutsuki</t>
+  </si>
+  <si>
+    <t>红叶</t>
+  </si>
+  <si>
+    <t>momiji</t>
+  </si>
+  <si>
+    <t>真守</t>
+  </si>
+  <si>
+    <t>mamori</t>
+  </si>
+  <si>
+    <t>樱花</t>
+  </si>
+  <si>
+    <t>ouka</t>
+  </si>
+  <si>
+    <t>琉璃</t>
+  </si>
+  <si>
+    <t>ruri</t>
+  </si>
+  <si>
+    <t>宵</t>
+  </si>
+  <si>
+    <t>yoi</t>
+  </si>
+  <si>
+    <t>琉奈</t>
+  </si>
+  <si>
+    <t>runa</t>
+  </si>
+  <si>
+    <t>律花</t>
+  </si>
+  <si>
+    <t>rikka</t>
+  </si>
+  <si>
+    <t>结城</t>
+  </si>
+  <si>
+    <t>yuuki</t>
   </si>
   <si>
     <t>技能等级</t>
@@ -211,46 +217,46 @@
     <t>普通</t>
   </si>
   <si>
-    <t>力裁斩击</t>
-  </si>
-  <si>
-    <t>力裁斩击：对对手造成8点直接伤害</t>
+    <t>烈焰一闪</t>
+  </si>
+  <si>
+    <t>烈焰一闪：对对手造成8点直接伤害</t>
   </si>
   <si>
     <t>强化</t>
   </si>
   <si>
-    <t>强化裁决</t>
-  </si>
-  <si>
-    <t>强化裁决：对对手造成16点直接伤害</t>
+    <t>烈焰裁决</t>
+  </si>
+  <si>
+    <t>烈焰裁决：对对手造成16点直接伤害</t>
   </si>
   <si>
     <t>解放</t>
   </si>
   <si>
-    <t>绝对裁决</t>
-  </si>
-  <si>
-    <t>绝对裁决：造成30点直接伤害并回复20点生命</t>
-  </si>
-  <si>
-    <t>镜像映射</t>
-  </si>
-  <si>
-    <t>镜像映射：摸2张牌并回复5点生命</t>
-  </si>
-  <si>
-    <t>镜像反击</t>
-  </si>
-  <si>
-    <t>镜像反击：摸3张牌并造成10点直接伤害</t>
-  </si>
-  <si>
-    <t>镜换轮转</t>
-  </si>
-  <si>
-    <t>镜换轮转：造成20点直接伤害，回复20点生命，摸2张牌</t>
+    <t>终末审判</t>
+  </si>
+  <si>
+    <t>终末审判：造成30点直接伤害并回复20点生命</t>
+  </si>
+  <si>
+    <t>镜影映射</t>
+  </si>
+  <si>
+    <t>镜影映射：摸2张牌并回复5点生命</t>
+  </si>
+  <si>
+    <t>镜影反击</t>
+  </si>
+  <si>
+    <t>镜影反击：摸3张牌并造成10点直接伤害</t>
+  </si>
+  <si>
+    <t>镜界轮回</t>
+  </si>
+  <si>
+    <t>镜界轮回：造成20点直接伤害，回复20点生命，摸2张牌</t>
   </si>
   <si>
     <t>虚拳引气</t>
@@ -265,16 +271,16 @@
     <t>引气冲拳：获得30点能量并造成8点直接伤害</t>
   </si>
   <si>
-    <t>空手相搏</t>
-  </si>
-  <si>
-    <t>空手相搏：造成20点直接伤害，回复20点生命，获得20点能量</t>
-  </si>
-  <si>
-    <t>噬渊之触</t>
-  </si>
-  <si>
-    <t>噬渊之触：造成6点直接伤害并汲取6点生命</t>
+    <t>空手搏斗</t>
+  </si>
+  <si>
+    <t>空手搏斗：造成20点直接伤害，回复20点生命，获得20点能量</t>
+  </si>
+  <si>
+    <t>深渊之触</t>
+  </si>
+  <si>
+    <t>深渊之触：造成6点直接伤害并汲取6点生命</t>
   </si>
   <si>
     <t>深渊噬魂</t>
@@ -283,10 +289,10 @@
     <t>深渊噬魂：造成14点直接伤害并汲取10点生命</t>
   </si>
   <si>
-    <t>渊噬万物</t>
-  </si>
-  <si>
-    <t>渊噬万物：造成28点直接伤害并汲取20点生命</t>
+    <t>暗噬万象</t>
+  </si>
+  <si>
+    <t>暗噬万象：造成28点直接伤害并汲取20点生命</t>
   </si>
   <si>
     <t>灼血冲击</t>
@@ -295,10 +301,10 @@
     <t>灼血冲击：造成10点直接伤害</t>
   </si>
   <si>
-    <t>烈焰灼血</t>
-  </si>
-  <si>
-    <t>烈焰灼血：造成20点直接伤害</t>
+    <t>血焰之舞</t>
+  </si>
+  <si>
+    <t>血焰之舞：造成20点直接伤害</t>
   </si>
   <si>
     <t>血焰爆发</t>
@@ -307,22 +313,22 @@
     <t>血焰爆发：造成40点直接伤害</t>
   </si>
   <si>
-    <t>殉道之愿</t>
-  </si>
-  <si>
-    <t>殉道之愿：回复10点生命</t>
-  </si>
-  <si>
-    <t>殉道之力</t>
-  </si>
-  <si>
-    <t>殉道之力：回复20点生命并获得10点能量</t>
-  </si>
-  <si>
-    <t>殉道解放</t>
-  </si>
-  <si>
-    <t>殉道解放：自动触发，濒死时回复30点生命并获得10点能量</t>
+    <t>圣女祈愿</t>
+  </si>
+  <si>
+    <t>圣女祈愿：回复10点生命</t>
+  </si>
+  <si>
+    <t>圣女加护</t>
+  </si>
+  <si>
+    <t>圣女加护：回复20点生命并获得10点能量</t>
+  </si>
+  <si>
+    <t>圣女降临</t>
+  </si>
+  <si>
+    <t>圣女降临：自动触发，濒死时回复30点生命并获得10点能量</t>
   </si>
   <si>
     <t>参数名称</t>
@@ -541,10 +547,10 @@
     <t>每个小人每阶段建造的进度（基础值）</t>
   </si>
   <si>
-    <t>一层房效率加成</t>
-  </si>
-  <si>
-    <t>超过1层房子时每层房子增加的工人效率</t>
+    <t>一层房工人加成</t>
+  </si>
+  <si>
+    <t>超过1层房子时每回合增加的工人数量</t>
   </si>
   <si>
     <t>二层房减伤</t>
@@ -644,6 +650,18 @@
   </si>
   <si>
     <t>节律者每次使用技能牌固定消耗的能量</t>
+  </si>
+  <si>
+    <t>解放首次命中伤害</t>
+  </si>
+  <si>
+    <t>四印解放后每回合首次命中造成的固定伤害</t>
+  </si>
+  <si>
+    <t>解放后续命中恢复</t>
+  </si>
+  <si>
+    <t>四印解放后每回合非首次命中时附加的恢复量</t>
   </si>
   <si>
     <t>场地名称</t>
@@ -1445,6 +1463,26 @@
         <v>33</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18">
+        <v>90</v>
+      </c>
+      <c r="D18">
+        <v>100</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -1465,42 +1503,42 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>11</v>
@@ -1521,7 +1559,7 @@
         <v>14</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3">
@@ -1529,10 +1567,10 @@
         <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D3">
         <v>10</v>
@@ -1541,7 +1579,7 @@
         <v>8</v>
       </c>
       <c r="J3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4">
@@ -1549,10 +1587,10 @@
         <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D4">
         <v>20</v>
@@ -1561,7 +1599,7 @@
         <v>16</v>
       </c>
       <c r="J4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5">
@@ -1569,10 +1607,10 @@
         <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D5">
         <v>80</v>
@@ -1584,7 +1622,7 @@
         <v>20</v>
       </c>
       <c r="J5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6">
@@ -1604,10 +1642,10 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D7">
         <v>8</v>
@@ -1619,7 +1657,7 @@
         <v>2</v>
       </c>
       <c r="J7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8">
@@ -1627,10 +1665,10 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D8">
         <v>16</v>
@@ -1642,7 +1680,7 @@
         <v>3</v>
       </c>
       <c r="J8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9">
@@ -1650,10 +1688,10 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D9">
         <v>80</v>
@@ -1668,7 +1706,7 @@
         <v>2</v>
       </c>
       <c r="J9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10">
@@ -1688,10 +1726,10 @@
         <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C11" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D11">
         <v>5</v>
@@ -1700,7 +1738,7 @@
         <v>20</v>
       </c>
       <c r="J11" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12">
@@ -1708,10 +1746,10 @@
         <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D12">
         <v>10</v>
@@ -1723,7 +1761,7 @@
         <v>30</v>
       </c>
       <c r="J12" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13">
@@ -1731,10 +1769,10 @@
         <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D13">
         <v>60</v>
@@ -1749,7 +1787,7 @@
         <v>20</v>
       </c>
       <c r="J13" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14">
@@ -1769,10 +1807,10 @@
         <v>23</v>
       </c>
       <c r="B15" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D15">
         <v>10</v>
@@ -1784,7 +1822,7 @@
         <v>6</v>
       </c>
       <c r="J15" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16">
@@ -1792,10 +1830,10 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D16">
         <v>20</v>
@@ -1807,7 +1845,7 @@
         <v>10</v>
       </c>
       <c r="J16" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -1815,10 +1853,10 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D17">
         <v>80</v>
@@ -1830,7 +1868,7 @@
         <v>20</v>
       </c>
       <c r="J17" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18">
@@ -1850,10 +1888,10 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C19" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D19">
         <v>10</v>
@@ -1862,7 +1900,7 @@
         <v>10</v>
       </c>
       <c r="J19" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20">
@@ -1870,10 +1908,10 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C20" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D20">
         <v>20</v>
@@ -1882,7 +1920,7 @@
         <v>20</v>
       </c>
       <c r="J20" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21">
@@ -1890,10 +1928,10 @@
         <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C21" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D21">
         <v>80</v>
@@ -1902,7 +1940,7 @@
         <v>40</v>
       </c>
       <c r="J21" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22">
@@ -1922,10 +1960,10 @@
         <v>27</v>
       </c>
       <c r="B23" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D23">
         <v>8</v>
@@ -1934,7 +1972,7 @@
         <v>10</v>
       </c>
       <c r="J23" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24">
@@ -1942,10 +1980,10 @@
         <v>27</v>
       </c>
       <c r="B24" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C24" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D24">
         <v>16</v>
@@ -1957,7 +1995,7 @@
         <v>10</v>
       </c>
       <c r="J24" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25">
@@ -1965,10 +2003,10 @@
         <v>27</v>
       </c>
       <c r="B25" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C25" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F25">
         <v>30</v>
@@ -1977,7 +2015,7 @@
         <v>10</v>
       </c>
       <c r="J25" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -1999,13 +2037,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2">
@@ -2013,13 +2051,13 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C2" t="s">
         <v>30</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3">
@@ -2027,13 +2065,13 @@
         <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4">
@@ -2041,13 +2079,13 @@
         <v>31</v>
       </c>
       <c r="B4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4" t="s">
         <v>110</v>
       </c>
-      <c r="C4" t="s">
-        <v>108</v>
-      </c>
       <c r="D4" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5">
@@ -2055,13 +2093,13 @@
         <v>31</v>
       </c>
       <c r="B5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6">
@@ -2069,13 +2107,13 @@
         <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7">
@@ -2083,13 +2121,13 @@
         <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8">
@@ -2097,13 +2135,13 @@
         <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9">
@@ -2111,13 +2149,13 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10">
@@ -2125,13 +2163,13 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C10" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11">
@@ -2145,13 +2183,13 @@
         <v>34</v>
       </c>
       <c r="B12" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C12" t="s">
         <v>30</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2159,13 +2197,13 @@
         <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C13" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="14">
@@ -2173,13 +2211,13 @@
         <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C14" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -2187,13 +2225,13 @@
         <v>34</v>
       </c>
       <c r="B15" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C15" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16">
@@ -2201,13 +2239,13 @@
         <v>34</v>
       </c>
       <c r="B16" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C16" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17">
@@ -2221,13 +2259,13 @@
         <v>36</v>
       </c>
       <c r="B18" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C18" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="19">
@@ -2235,13 +2273,13 @@
         <v>36</v>
       </c>
       <c r="B19" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C19" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20">
@@ -2249,13 +2287,13 @@
         <v>36</v>
       </c>
       <c r="B20" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C20" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="21">
@@ -2263,13 +2301,13 @@
         <v>36</v>
       </c>
       <c r="B21" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C21" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="22">
@@ -2277,13 +2315,13 @@
         <v>36</v>
       </c>
       <c r="B22" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C22" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="23">
@@ -2291,13 +2329,13 @@
         <v>36</v>
       </c>
       <c r="B23" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C23" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="24">
@@ -2305,13 +2343,13 @@
         <v>36</v>
       </c>
       <c r="B24" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C24" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="25">
@@ -2319,13 +2357,13 @@
         <v>36</v>
       </c>
       <c r="B25" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C25" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26">
@@ -2333,13 +2371,13 @@
         <v>36</v>
       </c>
       <c r="B26" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C26" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27">
@@ -2353,13 +2391,13 @@
         <v>38</v>
       </c>
       <c r="B28" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C28" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29">
@@ -2367,13 +2405,13 @@
         <v>38</v>
       </c>
       <c r="B29" t="s">
+        <v>123</v>
+      </c>
+      <c r="C29" t="s">
         <v>121</v>
       </c>
-      <c r="C29" t="s">
-        <v>119</v>
-      </c>
       <c r="D29" s="4" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30">
@@ -2381,13 +2419,13 @@
         <v>38</v>
       </c>
       <c r="B30" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C30" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="31">
@@ -2395,13 +2433,13 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C31" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="32">
@@ -2409,13 +2447,13 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="33">
@@ -2423,13 +2461,13 @@
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C33" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="34">
@@ -2437,13 +2475,13 @@
         <v>38</v>
       </c>
       <c r="B34" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C34" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="35">
@@ -2451,13 +2489,13 @@
         <v>38</v>
       </c>
       <c r="B35" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C35" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="36">
@@ -2471,13 +2509,13 @@
         <v>40</v>
       </c>
       <c r="B37" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C37" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="38">
@@ -2485,13 +2523,13 @@
         <v>40</v>
       </c>
       <c r="B38" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C38" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="39">
@@ -2499,13 +2537,13 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C39" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="40">
@@ -2513,13 +2551,13 @@
         <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C40" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="41">
@@ -2527,13 +2565,13 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C41" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="42">
@@ -2541,13 +2579,13 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C42" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="43">
@@ -2555,13 +2593,13 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C43" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="44">
@@ -2569,13 +2607,13 @@
         <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C44" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="45">
@@ -2589,13 +2627,13 @@
         <v>42</v>
       </c>
       <c r="B46" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C46" t="s">
         <v>30</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="47">
@@ -2603,13 +2641,13 @@
         <v>42</v>
       </c>
       <c r="B47" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C47" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="48">
@@ -2617,13 +2655,13 @@
         <v>42</v>
       </c>
       <c r="B48" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C48" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="49">
@@ -2637,13 +2675,13 @@
         <v>44</v>
       </c>
       <c r="B50" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C50" t="s">
         <v>30</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="51">
@@ -2651,13 +2689,13 @@
         <v>44</v>
       </c>
       <c r="B51" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C51" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="52">
@@ -2665,13 +2703,13 @@
         <v>44</v>
       </c>
       <c r="B52" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C52" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="53">
@@ -2679,13 +2717,13 @@
         <v>44</v>
       </c>
       <c r="B53" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C53" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="54">
@@ -2693,13 +2731,13 @@
         <v>44</v>
       </c>
       <c r="B54" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C54" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="55">
@@ -2713,13 +2751,13 @@
         <v>46</v>
       </c>
       <c r="B56" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C56" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="57">
@@ -2727,13 +2765,13 @@
         <v>46</v>
       </c>
       <c r="B57" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C57" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58">
@@ -2741,13 +2779,13 @@
         <v>46</v>
       </c>
       <c r="B58" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C58" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="59">
@@ -2755,13 +2793,13 @@
         <v>46</v>
       </c>
       <c r="B59" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C59" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="60">
@@ -2769,13 +2807,13 @@
         <v>46</v>
       </c>
       <c r="B60" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C60" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="61">
@@ -2789,13 +2827,47 @@
         <v>48</v>
       </c>
       <c r="B62" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C62" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>208</v>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3"/>
+      <c r="B63" s="3"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>50</v>
+      </c>
+      <c r="B64" t="s">
+        <v>211</v>
+      </c>
+      <c r="C64" t="s">
+        <v>156</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>50</v>
+      </c>
+      <c r="B65" t="s">
+        <v>213</v>
+      </c>
+      <c r="C65" t="s">
+        <v>121</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -2812,28 +2884,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2">
@@ -2850,7 +2922,7 @@
         <v>15</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>15</v>
@@ -2864,10 +2936,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="B3" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -2875,10 +2947,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="B4" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="C4" t="s">
         <v>30</v>
@@ -2889,10 +2961,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="B5" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -2903,10 +2975,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="B6" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -2914,10 +2986,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B7" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="E7">
         <v>2</v>
@@ -2925,10 +2997,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="B8" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="D8" t="s">
         <v>30</v>
@@ -2939,10 +3011,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="B9" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -2953,10 +3025,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="B10" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="E10">
         <v>0</v>

--- a/data/游戏配置表.xlsx
+++ b/data/游戏配置表.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="true" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FB4BAD5-51F2-43E2-AA40-5DBC74AE8B0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="31850" windowHeight="16110" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="角色属性" sheetId="1" r:id="rId1"/>
-    <sheet name="角色技能" sheetId="2" r:id="rId5"/>
-    <sheet name="特殊机制" sheetId="3" r:id="rId6"/>
-    <sheet name="场地效果" sheetId="4" r:id="rId7"/>
+    <sheet name="角色技能" sheetId="2" r:id="rId2"/>
+    <sheet name="特殊机制" sheetId="3" r:id="rId3"/>
+    <sheet name="场地效果" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="242">
   <si>
     <t>角色名称</t>
   </si>
@@ -737,35 +738,65 @@
   </si>
   <si>
     <t>protect</t>
+  </si>
+  <si>
+    <t>初始能量值</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>樱花</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color/>
-      <sz val="11"/>
     </font>
     <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF808080"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <i val="1"/>
-      <color rgb="FF808080"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color rgb="FF808080"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FF808080"/>
+    </font>
+    <font>
       <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="4">
@@ -795,39 +826,51 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color rgb="FF4472C4"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment wrapText="true"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true" applyAlignment="false">
-      <alignment/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment vertical="top" wrapText="true"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1083,17 +1126,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="14"/>
-    <col customWidth="true" max="2" min="2" width="16"/>
-    <col customWidth="true" max="6" min="3" width="10"/>
-    <col customWidth="true" max="9" min="7" width="14"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="6" width="10" customWidth="1"/>
+    <col min="7" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1122,7 +1165,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:9" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -1151,7 +1194,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1174,7 +1217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -1197,7 +1240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -1217,7 +1260,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -1237,7 +1280,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -1260,7 +1303,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -1283,7 +1326,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -1303,7 +1346,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>34</v>
       </c>
@@ -1323,7 +1366,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>36</v>
       </c>
@@ -1343,7 +1386,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>38</v>
       </c>
@@ -1363,7 +1406,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>40</v>
       </c>
@@ -1371,7 +1414,7 @@
         <v>41</v>
       </c>
       <c r="C13">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="D13">
         <v>100</v>
@@ -1383,7 +1426,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>42</v>
       </c>
@@ -1403,7 +1446,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>44</v>
       </c>
@@ -1423,7 +1466,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>46</v>
       </c>
@@ -1443,7 +1486,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>48</v>
       </c>
@@ -1463,7 +1506,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>50</v>
       </c>
@@ -1484,21 +1527,24 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:J25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.35"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="14"/>
-    <col customWidth="true" max="2" min="2" width="10"/>
-    <col customWidth="true" max="3" min="3" width="14"/>
-    <col customWidth="true" max="9" min="4" width="10"/>
-    <col customWidth="true" max="10" min="10" width="50"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1530,7 +1576,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>61</v>
       </c>
@@ -1562,7 +1608,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1582,7 +1628,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -1602,7 +1648,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -1625,7 +1671,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -1637,7 +1683,7 @@
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -1660,7 +1706,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -1683,7 +1729,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -1709,7 +1755,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -1721,7 +1767,7 @@
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
     </row>
-    <row r="11">
+    <row r="11" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -1741,7 +1787,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -1764,7 +1810,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -1790,7 +1836,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -1802,7 +1848,7 @@
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -1825,7 +1871,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -1848,7 +1894,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -1871,7 +1917,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -1883,7 +1929,7 @@
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
     </row>
-    <row r="19">
+    <row r="19" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -1903,7 +1949,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -1923,7 +1969,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -1943,7 +1989,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -1955,7 +2001,7 @@
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
     </row>
-    <row r="23">
+    <row r="23" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -1975,7 +2021,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -1998,7 +2044,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -2019,20 +2065,23 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:D66"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.35"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="14"/>
-    <col customWidth="true" max="2" min="2" width="20"/>
-    <col customWidth="true" max="3" min="3" width="16"/>
-    <col customWidth="true" max="4" min="4" width="40"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2046,7 +2095,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>31</v>
       </c>
@@ -2060,7 +2109,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -2074,12 +2123,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:4" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>31</v>
       </c>
-      <c r="B4" t="s">
-        <v>112</v>
+      <c r="B4" s="5" t="s">
+        <v>240</v>
       </c>
       <c r="C4" t="s">
         <v>110</v>
@@ -2088,7 +2137,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -2102,7 +2151,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>31</v>
       </c>
@@ -2116,7 +2165,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -2130,7 +2179,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>31</v>
       </c>
@@ -2144,7 +2193,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -2158,7 +2207,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -2172,13 +2221,13 @@
         <v>130</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>34</v>
       </c>
@@ -2192,7 +2241,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -2206,7 +2255,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -2220,7 +2269,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -2234,7 +2283,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>34</v>
       </c>
@@ -2248,13 +2297,13 @@
         <v>141</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18">
+    <row r="18" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>36</v>
       </c>
@@ -2268,7 +2317,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>36</v>
       </c>
@@ -2282,7 +2331,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -2296,7 +2345,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -2310,7 +2359,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -2324,7 +2373,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>36</v>
       </c>
@@ -2338,7 +2387,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>36</v>
       </c>
@@ -2352,7 +2401,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>36</v>
       </c>
@@ -2366,7 +2415,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>36</v>
       </c>
@@ -2380,13 +2429,13 @@
         <v>161</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28">
+    <row r="28" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>38</v>
       </c>
@@ -2400,7 +2449,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>38</v>
       </c>
@@ -2414,7 +2463,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>38</v>
       </c>
@@ -2428,7 +2477,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>38</v>
       </c>
@@ -2442,7 +2491,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>38</v>
       </c>
@@ -2456,7 +2505,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>38</v>
       </c>
@@ -2470,7 +2519,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>38</v>
       </c>
@@ -2484,7 +2533,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>38</v>
       </c>
@@ -2498,13 +2547,13 @@
         <v>172</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
     </row>
-    <row r="37">
+    <row r="37" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>40</v>
       </c>
@@ -2518,7 +2567,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>40</v>
       </c>
@@ -2532,7 +2581,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>40</v>
       </c>
@@ -2546,7 +2595,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>40</v>
       </c>
@@ -2560,7 +2609,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>40</v>
       </c>
@@ -2574,7 +2623,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>40</v>
       </c>
@@ -2588,7 +2637,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>40</v>
       </c>
@@ -2602,9 +2651,9 @@
         <v>168</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>40</v>
+    <row r="44" spans="1:4" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A44" s="5" t="s">
+        <v>241</v>
       </c>
       <c r="B44" t="s">
         <v>187</v>
@@ -2616,273 +2665,287 @@
         <v>188</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="3"/>
-      <c r="B45" s="3"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>42</v>
-      </c>
-      <c r="B46" t="s">
-        <v>131</v>
-      </c>
-      <c r="C46" t="s">
-        <v>30</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="47">
+    <row r="45" spans="1:4" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A45" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C45">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A46" s="3"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+    </row>
+    <row r="47" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>42</v>
       </c>
       <c r="B47" t="s">
-        <v>189</v>
+        <v>131</v>
       </c>
       <c r="C47" t="s">
-        <v>143</v>
+        <v>30</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="48">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="24" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>42</v>
       </c>
       <c r="B48" t="s">
+        <v>189</v>
+      </c>
+      <c r="C48" t="s">
+        <v>143</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>42</v>
+      </c>
+      <c r="B49" t="s">
         <v>191</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C49" t="s">
         <v>118</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D49" s="4" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="3"/>
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50" t="s">
-        <v>131</v>
-      </c>
-      <c r="C50" t="s">
-        <v>30</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="51">
+    <row r="50" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A50" s="3"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+    </row>
+    <row r="51" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>44</v>
       </c>
       <c r="B51" t="s">
-        <v>189</v>
+        <v>131</v>
       </c>
       <c r="C51" t="s">
-        <v>143</v>
+        <v>30</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="52">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="24" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>44</v>
       </c>
       <c r="B52" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C52" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="53">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>44</v>
       </c>
       <c r="B53" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C53" t="s">
         <v>153</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="54">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>44</v>
       </c>
       <c r="B54" t="s">
+        <v>195</v>
+      </c>
+      <c r="C54" t="s">
+        <v>153</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>44</v>
+      </c>
+      <c r="B55" t="s">
         <v>197</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C55" t="s">
         <v>118</v>
       </c>
-      <c r="D54" s="4" t="s">
+      <c r="D55" s="4" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="3"/>
-      <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>46</v>
-      </c>
-      <c r="B56" t="s">
-        <v>199</v>
-      </c>
-      <c r="C56" t="s">
-        <v>115</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="57">
+    <row r="56" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A56" s="3"/>
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+    </row>
+    <row r="57" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>46</v>
       </c>
       <c r="B57" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C57" t="s">
-        <v>153</v>
+        <v>115</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="58">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>46</v>
       </c>
       <c r="B58" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C58" t="s">
         <v>153</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="59">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>46</v>
       </c>
       <c r="B59" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C59" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="60">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>46</v>
       </c>
       <c r="B60" t="s">
+        <v>205</v>
+      </c>
+      <c r="C60" t="s">
+        <v>156</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>46</v>
+      </c>
+      <c r="B61" t="s">
         <v>207</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C61" t="s">
         <v>115</v>
       </c>
-      <c r="D60" s="4" t="s">
+      <c r="D61" s="4" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="3"/>
-      <c r="B61" s="3"/>
-      <c r="C61" s="3"/>
-      <c r="D61" s="3"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
+    <row r="62" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A62" s="3"/>
+      <c r="B62" s="3"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
+    </row>
+    <row r="63" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
         <v>48</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B63" t="s">
         <v>209</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C63" t="s">
         <v>174</v>
       </c>
-      <c r="D62" s="4" t="s">
+      <c r="D63" s="4" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="3"/>
-      <c r="B63" s="3"/>
-      <c r="C63" s="3"/>
-      <c r="D63" s="3"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="s">
-        <v>50</v>
-      </c>
-      <c r="B64" t="s">
-        <v>211</v>
-      </c>
-      <c r="C64" t="s">
-        <v>156</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="65">
+    <row r="64" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A64" s="3"/>
+      <c r="B64" s="3"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+    </row>
+    <row r="65" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>50</v>
       </c>
       <c r="B65" t="s">
+        <v>211</v>
+      </c>
+      <c r="C65" t="s">
+        <v>156</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>50</v>
+      </c>
+      <c r="B66" t="s">
         <v>213</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C66" t="s">
         <v>121</v>
       </c>
-      <c r="D65" s="4" t="s">
+      <c r="D66" s="4" t="s">
         <v>214</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.35"/>
   <cols>
-    <col customWidth="true" max="2" min="1" width="16"/>
-    <col customWidth="true" max="8" min="3" width="14"/>
+    <col min="1" max="2" width="16" customWidth="1"/>
+    <col min="3" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:8" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>215</v>
       </c>
@@ -2908,7 +2971,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:8" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -2934,7 +2997,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:8" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>224</v>
       </c>
@@ -2945,7 +3008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:8" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>226</v>
       </c>
@@ -2959,7 +3022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:8" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>228</v>
       </c>
@@ -2973,7 +3036,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:8" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>230</v>
       </c>
@@ -2984,7 +3047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:8" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>232</v>
       </c>
@@ -2995,7 +3058,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:8" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>234</v>
       </c>
@@ -3009,7 +3072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:8" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>236</v>
       </c>
@@ -3020,10 +3083,10 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>238</v>
       </c>
@@ -3038,5 +3101,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/游戏配置表.xlsx
+++ b/data/游戏配置表.xlsx
@@ -1,24 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FB4BAD5-51F2-43E2-AA40-5DBC74AE8B0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr filterPrivacy="true" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="31850" windowHeight="16110" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="角色属性" sheetId="1" r:id="rId1"/>
-    <sheet name="角色技能" sheetId="2" r:id="rId2"/>
-    <sheet name="特殊机制" sheetId="3" r:id="rId3"/>
-    <sheet name="场地效果" sheetId="4" r:id="rId4"/>
+    <sheet name="角色技能" sheetId="2" r:id="rId5"/>
+    <sheet name="特殊机制" sheetId="3" r:id="rId6"/>
+    <sheet name="场地效果" sheetId="4" r:id="rId7"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="242">
   <si>
     <t>角色名称</t>
   </si>
@@ -446,6 +445,9 @@
     <t>阶段3时攻击伤害倍率</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
     <t>受伤牌面加成阈值</t>
   </si>
   <si>
@@ -539,6 +541,9 @@
     <t>全免疫+反弹持续的阶段数</t>
   </si>
   <si>
+    <t>150</t>
+  </si>
+  <si>
     <t>工人基础效率</t>
   </si>
   <si>
@@ -738,65 +743,35 @@
   </si>
   <si>
     <t>protect</t>
-  </si>
-  <si>
-    <t>初始能量值</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>樱花</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
     <font>
-      <b/>
+      <family val="2"/>
+      <b val="1"/>
+      <color/>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
-      <i/>
+      <family val="2"/>
+      <i val="1"/>
+      <color rgb="FF808080"/>
       <sz val="10"/>
-      <color rgb="FF808080"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
+      <color rgb="FF808080"/>
       <sz val="9"/>
-      <color rgb="FF808080"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="4">
@@ -826,51 +801,39 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
         <color rgb="FF4472C4"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true" applyAlignment="false">
+      <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment vertical="top" wrapText="true"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1126,17 +1089,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="6" width="10" customWidth="1"/>
-    <col min="7" max="9" width="14" customWidth="1"/>
+    <col customWidth="true" max="1" min="1" width="14"/>
+    <col customWidth="true" max="2" min="2" width="16"/>
+    <col customWidth="true" max="6" min="3" width="10"/>
+    <col customWidth="true" max="9" min="7" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1165,7 +1128,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="2">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -1194,7 +1157,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1217,7 +1180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -1240,7 +1203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -1260,7 +1223,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -1280,7 +1243,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -1303,7 +1266,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -1326,7 +1289,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -1346,7 +1309,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10">
       <c r="A10" t="s">
         <v>34</v>
       </c>
@@ -1366,7 +1329,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11">
       <c r="A11" t="s">
         <v>36</v>
       </c>
@@ -1374,7 +1337,7 @@
         <v>37</v>
       </c>
       <c r="C11">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D11">
         <v>100</v>
@@ -1386,7 +1349,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12">
       <c r="A12" t="s">
         <v>38</v>
       </c>
@@ -1406,7 +1369,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13">
       <c r="A13" t="s">
         <v>40</v>
       </c>
@@ -1426,7 +1389,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14">
       <c r="A14" t="s">
         <v>42</v>
       </c>
@@ -1446,7 +1409,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15">
       <c r="A15" t="s">
         <v>44</v>
       </c>
@@ -1466,7 +1429,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16">
       <c r="A16" t="s">
         <v>46</v>
       </c>
@@ -1486,7 +1449,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17">
       <c r="A17" t="s">
         <v>48</v>
       </c>
@@ -1506,7 +1469,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18">
       <c r="A18" t="s">
         <v>50</v>
       </c>
@@ -1527,24 +1490,21 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J25"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="50" customWidth="1"/>
+    <col customWidth="true" max="1" min="1" width="14"/>
+    <col customWidth="true" max="2" min="2" width="10"/>
+    <col customWidth="true" max="3" min="3" width="14"/>
+    <col customWidth="true" max="9" min="4" width="10"/>
+    <col customWidth="true" max="10" min="10" width="50"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1576,7 +1536,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="2">
       <c r="A2" s="2" t="s">
         <v>61</v>
       </c>
@@ -1608,7 +1568,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1628,7 +1588,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="4">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -1648,7 +1608,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="5">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -1671,7 +1631,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="6">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -1683,7 +1643,7 @@
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
     </row>
-    <row r="7" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="7">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -1706,7 +1666,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="8">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -1729,7 +1689,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="9">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -1755,7 +1715,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="10">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -1767,7 +1727,7 @@
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
     </row>
-    <row r="11" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="11">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -1787,7 +1747,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="12">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -1810,7 +1770,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="13">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -1836,7 +1796,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="14">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -1848,7 +1808,7 @@
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
     </row>
-    <row r="15" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="15">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -1871,7 +1831,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="16">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -1894,7 +1854,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="17">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -1917,7 +1877,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="18">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -1929,7 +1889,7 @@
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
     </row>
-    <row r="19" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="19">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -1949,7 +1909,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="20">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -1969,7 +1929,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="21">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -1989,7 +1949,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="22">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -2001,7 +1961,7 @@
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
     </row>
-    <row r="23" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="23">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -2021,7 +1981,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="24">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -2044,7 +2004,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="25">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -2065,23 +2025,20 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D66"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="40" customWidth="1"/>
+    <col customWidth="true" max="1" min="1" width="14"/>
+    <col customWidth="true" max="2" min="2" width="20"/>
+    <col customWidth="true" max="3" min="3" width="16"/>
+    <col customWidth="true" max="4" min="4" width="40"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2095,7 +2052,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="2">
       <c r="A2" t="s">
         <v>31</v>
       </c>
@@ -2109,7 +2066,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="3">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -2123,12 +2080,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="4">
       <c r="A4" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>240</v>
+      <c r="B4" t="s">
+        <v>112</v>
       </c>
       <c r="C4" t="s">
         <v>110</v>
@@ -2137,7 +2094,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="5">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -2151,7 +2108,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="6">
       <c r="A6" t="s">
         <v>31</v>
       </c>
@@ -2165,7 +2122,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="7">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -2179,7 +2136,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="8">
       <c r="A8" t="s">
         <v>31</v>
       </c>
@@ -2193,7 +2150,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="9">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -2207,7 +2164,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="10">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -2221,13 +2178,13 @@
         <v>130</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="11">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="12">
       <c r="A12" t="s">
         <v>34</v>
       </c>
@@ -2241,7 +2198,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="13">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -2255,7 +2212,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="14">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -2269,7 +2226,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="15">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -2283,7 +2240,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="16">
       <c r="A16" t="s">
         <v>34</v>
       </c>
@@ -2297,681 +2254,723 @@
         <v>141</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="17">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="18">
       <c r="A18" t="s">
         <v>36</v>
       </c>
       <c r="B18" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="C18" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19" t="s">
         <v>36</v>
       </c>
       <c r="B19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C19" t="s">
         <v>142</v>
       </c>
-      <c r="C19" t="s">
-        <v>143</v>
-      </c>
       <c r="D19" s="4" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20" t="s">
         <v>36</v>
       </c>
       <c r="B20" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="C20" t="s">
         <v>115</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21" t="s">
         <v>36</v>
       </c>
       <c r="B21" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C21" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22" t="s">
         <v>36</v>
       </c>
       <c r="B22" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C22" t="s">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23" t="s">
         <v>36</v>
       </c>
       <c r="B23" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C23" t="s">
-        <v>153</v>
+        <v>124</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24" t="s">
         <v>36</v>
       </c>
       <c r="B24" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C24" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25" t="s">
         <v>36</v>
       </c>
       <c r="B25" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C25" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="26">
       <c r="A26" t="s">
         <v>36</v>
       </c>
       <c r="B26" t="s">
+        <v>156</v>
+      </c>
+      <c r="C26" t="s">
+        <v>157</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27" t="s">
+        <v>159</v>
+      </c>
+      <c r="C27" t="s">
+        <v>154</v>
+      </c>
+      <c r="D27" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="C26" t="s">
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" t="s">
+        <v>161</v>
+      </c>
+      <c r="C28" t="s">
         <v>118</v>
       </c>
-      <c r="D26" s="4" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-    </row>
-    <row r="28" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" t="s">
-        <v>120</v>
-      </c>
-      <c r="C28" t="s">
-        <v>153</v>
-      </c>
       <c r="D28" s="4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" t="s">
-        <v>123</v>
-      </c>
-      <c r="C29" t="s">
-        <v>121</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+    </row>
+    <row r="30">
       <c r="A30" t="s">
         <v>38</v>
       </c>
       <c r="B30" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="C30" t="s">
-        <v>115</v>
+        <v>154</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="31">
       <c r="A31" t="s">
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>162</v>
+        <v>123</v>
       </c>
       <c r="C31" t="s">
-        <v>163</v>
+        <v>121</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="32">
       <c r="A32" t="s">
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>165</v>
+        <v>126</v>
       </c>
       <c r="C32" t="s">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="33">
       <c r="A33" t="s">
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C33" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="34">
       <c r="A34" t="s">
         <v>38</v>
       </c>
       <c r="B34" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C34" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="35">
       <c r="A35" t="s">
         <v>38</v>
       </c>
       <c r="B35" t="s">
+        <v>168</v>
+      </c>
+      <c r="C35" t="s">
+        <v>151</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" t="s">
+        <v>170</v>
+      </c>
+      <c r="C36" t="s">
+        <v>115</v>
+      </c>
+      <c r="D36" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="C35" t="s">
-        <v>153</v>
-      </c>
-      <c r="D35" s="4" t="s">
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A36" s="3"/>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-    </row>
-    <row r="37" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>40</v>
-      </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
+        <v>154</v>
+      </c>
+      <c r="D37" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="C37" t="s">
-        <v>174</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" t="s">
-        <v>176</v>
-      </c>
-      <c r="C38" t="s">
-        <v>118</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="38">
+      <c r="A38" s="3"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+    </row>
+    <row r="39">
       <c r="A39" t="s">
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>178</v>
+        <v>109</v>
       </c>
       <c r="C39" t="s">
-        <v>118</v>
+        <v>174</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="40">
       <c r="A40" t="s">
         <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>180</v>
+        <v>112</v>
       </c>
       <c r="C40" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="41">
       <c r="A41" t="s">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="C41" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="42">
       <c r="A42" t="s">
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C42" t="s">
-        <v>163</v>
+        <v>118</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="43">
       <c r="A43" t="s">
         <v>40</v>
       </c>
       <c r="B43" t="s">
+        <v>180</v>
+      </c>
+      <c r="C43" t="s">
+        <v>118</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>40</v>
+      </c>
+      <c r="B44" t="s">
+        <v>182</v>
+      </c>
+      <c r="C44" t="s">
+        <v>164</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" t="s">
+        <v>184</v>
+      </c>
+      <c r="C45" t="s">
+        <v>157</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" t="s">
         <v>186</v>
       </c>
-      <c r="C43" t="s">
-        <v>156</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A44" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="B44" t="s">
+      <c r="C46" t="s">
+        <v>164</v>
+      </c>
+      <c r="D46" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="C44" t="s">
-        <v>150</v>
-      </c>
-      <c r="D44" s="4" t="s">
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A45" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="C45">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A46" s="3"/>
-      <c r="B46" s="3"/>
-      <c r="C46" s="3"/>
-      <c r="D46" s="3"/>
-    </row>
-    <row r="47" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" t="s">
-        <v>131</v>
-      </c>
       <c r="C47" t="s">
-        <v>30</v>
+        <v>157</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" ht="24" x14ac:dyDescent="0.35">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="48">
       <c r="A48" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B48" t="s">
         <v>189</v>
       </c>
       <c r="C48" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
+    <row r="49">
+      <c r="A49" s="3"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
         <v>42</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B50" t="s">
+        <v>131</v>
+      </c>
+      <c r="C50" t="s">
+        <v>30</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>42</v>
+      </c>
+      <c r="B51" t="s">
         <v>191</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C51" t="s">
+        <v>144</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>42</v>
+      </c>
+      <c r="B52" t="s">
+        <v>193</v>
+      </c>
+      <c r="C52" t="s">
         <v>118</v>
       </c>
-      <c r="D49" s="4" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A50" s="3"/>
-      <c r="B50" s="3"/>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
-    </row>
-    <row r="51" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
-        <v>44</v>
-      </c>
-      <c r="B51" t="s">
-        <v>131</v>
-      </c>
-      <c r="C51" t="s">
-        <v>30</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="24" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
-        <v>44</v>
-      </c>
-      <c r="B52" t="s">
-        <v>189</v>
-      </c>
-      <c r="C52" t="s">
-        <v>143</v>
-      </c>
       <c r="D52" s="4" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
-        <v>44</v>
-      </c>
-      <c r="B53" t="s">
-        <v>193</v>
-      </c>
-      <c r="C53" t="s">
-        <v>153</v>
-      </c>
-      <c r="D53" s="4" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="53">
+      <c r="A53" s="3"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+    </row>
+    <row r="54">
       <c r="A54" t="s">
         <v>44</v>
       </c>
       <c r="B54" t="s">
-        <v>195</v>
+        <v>131</v>
       </c>
       <c r="C54" t="s">
-        <v>153</v>
+        <v>30</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="55">
       <c r="A55" t="s">
         <v>44</v>
       </c>
       <c r="B55" t="s">
+        <v>191</v>
+      </c>
+      <c r="C55" t="s">
+        <v>144</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>44</v>
+      </c>
+      <c r="B56" t="s">
+        <v>195</v>
+      </c>
+      <c r="C56" t="s">
+        <v>154</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>44</v>
+      </c>
+      <c r="B57" t="s">
         <v>197</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C57" t="s">
+        <v>154</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>44</v>
+      </c>
+      <c r="B58" t="s">
+        <v>199</v>
+      </c>
+      <c r="C58" t="s">
         <v>118</v>
       </c>
-      <c r="D55" s="4" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A56" s="3"/>
-      <c r="B56" s="3"/>
-      <c r="C56" s="3"/>
-      <c r="D56" s="3"/>
-    </row>
-    <row r="57" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
-        <v>46</v>
-      </c>
-      <c r="B57" t="s">
-        <v>199</v>
-      </c>
-      <c r="C57" t="s">
-        <v>115</v>
-      </c>
-      <c r="D57" s="4" t="s">
+      <c r="D58" s="4" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
-        <v>46</v>
-      </c>
-      <c r="B58" t="s">
-        <v>201</v>
-      </c>
-      <c r="C58" t="s">
-        <v>153</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
-        <v>46</v>
-      </c>
-      <c r="B59" t="s">
-        <v>203</v>
-      </c>
-      <c r="C59" t="s">
-        <v>153</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="59">
+      <c r="A59" s="3"/>
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+    </row>
+    <row r="60">
       <c r="A60" t="s">
         <v>46</v>
       </c>
       <c r="B60" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C60" t="s">
-        <v>156</v>
+        <v>115</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="61">
       <c r="A61" t="s">
         <v>46</v>
       </c>
       <c r="B61" t="s">
+        <v>203</v>
+      </c>
+      <c r="C61" t="s">
+        <v>154</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>46</v>
+      </c>
+      <c r="B62" t="s">
+        <v>205</v>
+      </c>
+      <c r="C62" t="s">
+        <v>154</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>46</v>
+      </c>
+      <c r="B63" t="s">
         <v>207</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C63" t="s">
+        <v>157</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>46</v>
+      </c>
+      <c r="B64" t="s">
+        <v>209</v>
+      </c>
+      <c r="C64" t="s">
         <v>115</v>
       </c>
-      <c r="D61" s="4" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A62" s="3"/>
-      <c r="B62" s="3"/>
-      <c r="C62" s="3"/>
-      <c r="D62" s="3"/>
-    </row>
-    <row r="63" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
+      <c r="D64" s="4" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3"/>
+      <c r="B65" s="3"/>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
         <v>48</v>
       </c>
-      <c r="B63" t="s">
-        <v>209</v>
-      </c>
-      <c r="C63" t="s">
-        <v>174</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A64" s="3"/>
-      <c r="B64" s="3"/>
-      <c r="C64" s="3"/>
-      <c r="D64" s="3"/>
-    </row>
-    <row r="65" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
+      <c r="B66" t="s">
+        <v>211</v>
+      </c>
+      <c r="C66" t="s">
+        <v>176</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3"/>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
         <v>50</v>
       </c>
-      <c r="B65" t="s">
-        <v>211</v>
-      </c>
-      <c r="C65" t="s">
-        <v>156</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
+      <c r="B68" t="s">
+        <v>213</v>
+      </c>
+      <c r="C68" t="s">
+        <v>157</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
         <v>50</v>
       </c>
-      <c r="B66" t="s">
-        <v>213</v>
-      </c>
-      <c r="C66" t="s">
+      <c r="B69" t="s">
+        <v>215</v>
+      </c>
+      <c r="C69" t="s">
         <v>121</v>
       </c>
-      <c r="D66" s="4" t="s">
-        <v>214</v>
+      <c r="D69" s="4" t="s">
+        <v>216</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
   <cols>
-    <col min="1" max="2" width="16" customWidth="1"/>
-    <col min="3" max="8" width="14" customWidth="1"/>
+    <col customWidth="true" max="2" min="1" width="16"/>
+    <col customWidth="true" max="8" min="3" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="26.5" x14ac:dyDescent="0.35">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -2985,7 +2984,7 @@
         <v>15</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>15</v>
@@ -2997,23 +2996,23 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="3">
       <c r="A3" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="4">
       <c r="A4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B4" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C4" t="s">
         <v>30</v>
@@ -3022,12 +3021,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="5">
       <c r="A5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B5" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -3036,34 +3035,34 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="6">
       <c r="A6" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="7">
       <c r="A7" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B7" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E7">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="8">
       <c r="A8" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B8" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D8" t="s">
         <v>30</v>
@@ -3072,26 +3071,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="9">
       <c r="A9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="14.5" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B10" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -3101,7 +3100,5 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>